--- a/data/rules/riskClassification.xlsx
+++ b/data/rules/riskClassification.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BD35A6-8842-4E8E-9F69-71825930274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCF8939-57F6-462C-B3E1-9321F7143CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="150">
   <si>
     <t>Indicator</t>
   </si>
@@ -468,6 +468,12 @@
   </si>
   <si>
     <t>Nuclear</t>
+  </si>
+  <si>
+    <t>SECO-SANCTIONS</t>
+  </si>
+  <si>
+    <t>Financial sanctions (asset freeze)</t>
   </si>
 </sst>
 </file>
@@ -867,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.6328125" style="9" customWidth="1"/>
@@ -1158,6 +1164,26 @@
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/rules/riskClassification.xlsx
+++ b/data/rules/riskClassification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCF8939-57F6-462C-B3E1-9321F7143CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE69FE4-E63D-4326-AFC6-38D36126BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
   <si>
     <t>Indicator</t>
   </si>
@@ -474,6 +474,18 @@
   </si>
   <si>
     <t>Financial sanctions (asset freeze)</t>
+  </si>
+  <si>
+    <t>FBI-WANTED</t>
+  </si>
+  <si>
+    <t>US federal wanted persons / fugitives</t>
+  </si>
+  <si>
+    <t>Law Enforcement</t>
+  </si>
+  <si>
+    <t>Wanted / Investigation</t>
   </si>
 </sst>
 </file>
@@ -873,14 +885,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.6328125" style="9" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.36328125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" style="9" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" style="9" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="35" style="8" customWidth="1"/>
   </cols>
@@ -1185,8 +1197,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/rules/riskClassification.xlsx
+++ b/data/rules/riskClassification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE69FE4-E63D-4326-AFC6-38D36126BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1141F4D7-B543-441A-8A3D-20CF7FC74AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListScope" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="170">
   <si>
     <t>Indicator</t>
   </si>
@@ -486,6 +486,54 @@
   </si>
   <si>
     <t>Wanted / Investigation</t>
+  </si>
+  <si>
+    <t>Tax Evasion</t>
+  </si>
+  <si>
+    <t>Wilful evasion of taxes or customs duties — under-declaring income, fraudulent returns, or hiding assets from tax authorities. Under PH AMLA a predicate crime only above a large deficiency-tax threshold with fraud. Cues: tax evasion, tax fraud, undeclared income, BIR case.</t>
+  </si>
+  <si>
+    <t>Environmental Crime</t>
+  </si>
+  <si>
+    <t>Illegal exploitation of natural resources — illegal logging, mining, fishing, or wildlife trafficking. Cues: illegal logging/mining/fishing, wildlife trafficking, forestry/fisheries/mining code violation.</t>
+  </si>
+  <si>
+    <t>Counterfeiting &amp; Forgery</t>
+  </si>
+  <si>
+    <t>Producing or dealing in forged or counterfeit documents, currency, goods, or financial instruments. Cues: counterfeit currency/goods, forged documents, falsification.</t>
+  </si>
+  <si>
+    <t>Smuggling</t>
+  </si>
+  <si>
+    <t>Illicit cross-border movement of goods to evade customs duties or controls.</t>
+  </si>
+  <si>
+    <t>Extortion</t>
+  </si>
+  <si>
+    <t>Obtaining money or property through threats, coercion, or protection rackets.</t>
+  </si>
+  <si>
+    <t>Illegal Gambling</t>
+  </si>
+  <si>
+    <t>Operating or profiting from unlawful gambling (e.g. jueteng, masiao, unlicensed betting).</t>
+  </si>
+  <si>
+    <t>Kidnapping for Ransom</t>
+  </si>
+  <si>
+    <t>Abduction of persons to extort ransom payments.</t>
+  </si>
+  <si>
+    <t>Terrorism Financing</t>
+  </si>
+  <si>
+    <t>Providing or collecting funds, assets, or material support for terrorism or terrorist groups.</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="30" style="6" customWidth="1"/>
@@ -1330,103 +1378,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>104</v>
+      <c r="C5" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1441,69 +1489,105 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C12" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>122</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
+    <sortCondition ref="B1:B20"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.1796875" style="5" customWidth="1"/>
@@ -1634,115 +1718,173 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>46</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C26">
+    <sortCondition ref="B1:B26"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/rules/riskClassification.xlsx
+++ b/data/rules/riskClassification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1141F4D7-B543-441A-8A3D-20CF7FC74AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0068F045-2373-4355-8375-13EE0394124A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListScope" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="190">
   <si>
     <t>Indicator</t>
   </si>
@@ -534,19 +534,84 @@
   </si>
   <si>
     <t>Providing or collecting funds, assets, or material support for terrorism or terrorist groups.</t>
+  </si>
+  <si>
+    <t>DILG-LOCAL-OFFICIALS</t>
+  </si>
+  <si>
+    <t>PH local government officials</t>
+  </si>
+  <si>
+    <t>CFTC-RED-LIST</t>
+  </si>
+  <si>
+    <t>US CFTC Registration Deficient List</t>
+  </si>
+  <si>
+    <t>Foreign firms soliciting US persons unregistered</t>
+  </si>
+  <si>
+    <t>GPPB-BLACKLISTED-ENTITIES</t>
+  </si>
+  <si>
+    <t>PH govt procurement blacklist</t>
+  </si>
+  <si>
+    <t>Blacklisted from government procurement</t>
+  </si>
+  <si>
+    <t>Elected/appointed LGU officials 2025-2028</t>
+  </si>
+  <si>
+    <t>DMW-RECRUITMENT-AGENCIES</t>
+  </si>
+  <si>
+    <t>Adverse handled by rules on license status</t>
+  </si>
+  <si>
+    <t>MeasureNote</t>
+  </si>
+  <si>
+    <t>Forever Banned</t>
+  </si>
+  <si>
+    <t>Revoked</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Suspen</t>
+  </si>
+  <si>
+    <t>PH licensed recruitment agencies</t>
+  </si>
+  <si>
+    <t>regex</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -605,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -653,6 +718,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,19 +999,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42.6328125" style="9" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="2" customWidth="1"/>
     <col min="3" max="3" width="32.81640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="27.26953125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.81640625" style="9" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35" style="8" customWidth="1"/>
+    <col min="7" max="7" width="40.36328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>47</v>
       </c>
@@ -968,7 +1034,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>54</v>
       </c>
@@ -988,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>59</v>
       </c>
@@ -1011,7 +1077,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
         <v>62</v>
       </c>
@@ -1031,7 +1097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>64</v>
       </c>
@@ -1051,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
         <v>66</v>
       </c>
@@ -1071,7 +1137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>68</v>
       </c>
@@ -1091,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
         <v>70</v>
       </c>
@@ -1111,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="A9" s="6" t="s">
         <v>72</v>
       </c>
@@ -1131,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>74</v>
       </c>
@@ -1151,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -1171,7 +1237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="29" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>78</v>
       </c>
@@ -1191,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -1211,7 +1277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
         <v>79</v>
       </c>
@@ -1225,7 +1291,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7">
       <c r="A15" s="9" t="s">
         <v>148</v>
       </c>
@@ -1245,7 +1311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7">
       <c r="A16" s="9" t="s">
         <v>150</v>
       </c>
@@ -1263,6 +1329,89 @@
       </c>
       <c r="F16" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1274,13 +1423,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="31.54296875" style="7" customWidth="1"/>
     <col min="2" max="2" width="92.36328125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>82</v>
       </c>
@@ -1288,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
         <v>57</v>
       </c>
@@ -1297,7 +1446,7 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
         <v>84</v>
       </c>
@@ -1305,7 +1454,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
         <v>86</v>
       </c>
@@ -1313,7 +1462,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" s="7" t="s">
         <v>76</v>
       </c>
@@ -1321,7 +1470,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
@@ -1329,7 +1478,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" s="7" t="s">
         <v>91</v>
       </c>
@@ -1337,7 +1486,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
         <v>93</v>
       </c>
@@ -1345,7 +1494,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="29">
       <c r="A9" s="7" t="s">
         <v>95</v>
       </c>
@@ -1361,13 +1510,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="30" style="6" customWidth="1"/>
     <col min="3" max="3" width="70.26953125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="14" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>97</v>
       </c>
@@ -1378,7 +1527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="29">
       <c r="A2" s="6" t="s">
         <v>121</v>
       </c>
@@ -1389,7 +1538,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="58" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
@@ -1400,7 +1549,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="58" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>158</v>
       </c>
@@ -1411,7 +1560,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="43.5">
       <c r="A5" s="5" t="s">
         <v>114</v>
       </c>
@@ -1422,7 +1571,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="58" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>156</v>
       </c>
@@ -1433,7 +1582,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="43.5" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
@@ -1444,7 +1593,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="72.5" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
@@ -1455,7 +1604,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="58" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>107</v>
       </c>
@@ -1466,7 +1615,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="29" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>32</v>
       </c>
@@ -1477,7 +1626,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="31.5" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>112</v>
       </c>
@@ -1488,7 +1637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="43.5" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>154</v>
       </c>
@@ -1499,7 +1648,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="72.5">
       <c r="A13" s="6" t="s">
         <v>77</v>
       </c>
@@ -1510,7 +1659,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="43.5">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -1521,7 +1670,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="43.5" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>117</v>
       </c>
@@ -1532,7 +1681,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="58">
       <c r="A16" s="6" t="s">
         <v>100</v>
       </c>
@@ -1543,7 +1692,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="58">
       <c r="A17" s="6" t="s">
         <v>102</v>
       </c>
@@ -1554,7 +1703,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
         <v>25</v>
       </c>
@@ -1565,7 +1714,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
         <v>58</v>
       </c>
@@ -1588,14 +1737,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="32.1796875" style="5" customWidth="1"/>
     <col min="2" max="2" width="18.453125" style="5" customWidth="1"/>
     <col min="3" max="3" width="61.54296875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="14" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1606,7 +1755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="64" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1617,7 +1766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="43.5" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1628,7 +1777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="43.5" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1639,7 +1788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="58" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1650,7 +1799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="43.5" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1661,7 +1810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="43.5" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1672,7 +1821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="43.5" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
@@ -1683,7 +1832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="43.5" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
@@ -1694,7 +1843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="43.5" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -1705,7 +1854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="43.5" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1716,7 +1865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -1727,7 +1876,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
@@ -1738,7 +1887,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
@@ -1749,7 +1898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
         <v>45</v>
       </c>
@@ -1760,7 +1909,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1771,7 +1920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -1782,7 +1931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
@@ -1793,7 +1942,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="29">
       <c r="A19" s="5" t="s">
         <v>160</v>
       </c>
@@ -1804,7 +1953,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="29">
       <c r="A20" s="5" t="s">
         <v>162</v>
       </c>
@@ -1815,7 +1964,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="29">
       <c r="A21" s="5" t="s">
         <v>164</v>
       </c>
@@ -1826,7 +1975,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
         <v>166</v>
       </c>
@@ -1837,7 +1986,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1848,7 +1997,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
@@ -1859,7 +2008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
         <v>29</v>
       </c>
@@ -1870,7 +2019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="29">
       <c r="A26" s="5" t="s">
         <v>168</v>
       </c>
@@ -1891,11 +2040,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.6328125" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" style="9" customWidth="1"/>
     <col min="5" max="5" width="10.90625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.7265625" style="2" customWidth="1"/>
@@ -1905,7 +2054,7 @@
     <col min="10" max="10" width="8.7265625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="13" customFormat="1">
       <c r="A1" s="11" t="s">
         <v>123</v>
       </c>
@@ -1935,7 +2084,7 @@
       </c>
       <c r="J1" s="12"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>131</v>
       </c>
@@ -1964,7 +2113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>136</v>
       </c>
@@ -1993,7 +2142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>138</v>
       </c>
@@ -2022,7 +2171,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -2051,7 +2200,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>143</v>
       </c>
@@ -2080,7 +2229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>145</v>
       </c>
@@ -2109,8 +2258,95 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F16" s="10"/>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="2">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="2">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="F14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
